--- a/output/(山本)整合性_一貫性_再構成.xlsx
+++ b/output/(山本)整合性_一貫性_再構成.xlsx
@@ -461,13 +461,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>システムが受け取る入力値、起動条件、または特定のイベント（原因）に対し、それによって引き起こされる状態遷移や出力結果（結果）を、一意に特定できる形式で矛盾なく記述している。</t>
+          <t>例外処理や状態遷移などの仕様において、システムの挙動（結果）と、そのトリガーとなる入力条件やイベント（原因）を、エラー定義表や状態遷移表に基づいて一対一で対応させて記述している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】認証エラー発生時、ログイン画面に戻る場合とエラー画面を表示する場合がある（箇所により対応が不整合）。
-→【適合例】認証エラー発生時は、一貫してエラーコード「E001」をダイアログ表示し、ログイン画面へ遷移する。</t>
+          <t>★新規追加
+【非適合例】「API通信エラー時は、リトライ処理を実行するかエラー画面へ遷移する。」と記述している。（通信エラーの具体的な原因と、それに対するシステムの挙動が対応していない。）
+→【適合例】「API通信エラー発生時について、タイムアウト時は最大3回のリトライ処理を行い、認証エラー時は即時エラー画面へ遷移する。」と、エラー原因ごとにシステムの挙動を対応させて記述している。</t>
         </is>
       </c>
     </row>
@@ -479,14 +480,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>設計上の決定事項や技術選定に対し、代替案との比較、技術的制約、または非機能要件等の上位文書とのトレーサビリティに基づく客観的な選定理由を明記している。</t>
+          <t>アーキテクチャ選定や機能仕様の決定事項に対して、その方式を採用した技術的理由や、非機能要件に基づく評価の根拠を明記している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】DBサーバーにはPostgreSQLを採用する（選定理由が不明）。
-→【適合例】同時実行制御の要件を満たし、かつライセンスコストを抑制するため、オープンソースのPostgreSQLをDBサーバーに採用する。</t>
+【非適合例】ユーザー認証機能には、OAuth2.0による外部プロバイダ認証を採用する。（採用理由の記述がない。）
+→【適合例】ユーザー認証機能には、既存の社内システムとの統合によるシングルサインオンを実現し、運用コストを削減するため、OAuth2.0による外部プロバイダ認証を採用する。</t>
         </is>
       </c>
     </row>
@@ -498,13 +499,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ビジネスプロセス、プログラムの実行フロー、またはデータのライフサイクルを、時間の経過や論理的な実行ステップに従って、読み手が迷わないよう順序立てて記述している。</t>
+          <t>処理フローや状態遷移の説明において、システムの実行順序や時間の経過に沿って、業務フロー図やシーケンス図と整合する時系列で手順を展開して記述している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】データ更新後にログイン確認を行い、その前に入力内容のチェックを行う（処理手順が実行順序と一致していない）。
-→【適合例】1.入力内容をチェックする。2.ユーザーの権限を確認する。3.DBのデータを更新する。</t>
+          <t>★新規追加
+【非適合例】会員登録処理では、完了メールを送信する。その前にDBへユーザー情報をInsertするが、パスワードはハッシュ化しておく。（処理手順が順不同で記述されており、時間の経過に沿っていない。）
+→【適合例】会員登録処理では、まずパスワードをハッシュ化し、次にDBへユーザー情報をInsertする。登録成功後に、完了メールを送信する。</t>
         </is>
       </c>
     </row>
@@ -516,13 +518,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>章、節、または項の冒頭において、その単位の目的、結論、または記述範囲の全体像を要約として提示し、その後に補足情報や技術的詳細を展開する構成をとっている。</t>
+          <t>文書や章の冒頭において、システム構成図や業務フロー図を用いて全体像を提示した上で、その構成要素に関する個別の詳細仕様を記述している。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】（3ページにわたる技術解説の末尾に）以上より、本機能のAPI実装は不要と判断する（結論が後回しで意図が不明）。
-→【適合例】本章では、既存APIの再利用性について検討した結果、新規開発を不要とする判断に至った経緯を述べる。詳細は以下の通りである。</t>
+          <t>★新規追加
+【非適合例】第2章の冒頭から、特定のAPIのパラメータ定義やDBのテーブル定義を羅列している。（全体構成が提示されず、詳細仕様が先行している。）
+→【適合例】第2章の冒頭でシステム全体のアーキテクチャ図とコンポーネント間の連携フローを提示した後に、各コンポーネントのAPI定義やテーブル定義の詳細を記述している。</t>
         </is>
       </c>
     </row>
@@ -534,14 +537,14 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>各段落（パラグラフ）の冒頭に、その段落で最も伝えたい要点を記した主題文（トピックセンテンス）を配置し、後続の文でその具体例や根拠を補足する構造を維持している。</t>
+          <t>各段落の記述において、最初の文でシステム要件の結論や主題を明示し、続く文でその選定理由や具体的な処理方式を補足するパラグラフライティングの原則に基づいて記述している。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】バックアップは毎日2時に行う。容量は10GBである。リストアテストも月次で実施する（単なる事実の羅列で要点が不明）。
-→【適合例】データ保守運用は、可用性と整合性を重視して設計する。具体的には、毎日午前2時のフルバックアップに加え、月次でのリストア検証を必須とする。</t>
+【非適合例】当システムは夜間バッチで大量データを処理する。既存のRDBではIOボトルネックが発生する。そのため、新たにインメモリDBを導入してパフォーマンスを向上させる。（主題である結論が段落の最後に配置されている。）
+→【適合例】当システムはパフォーマンス向上のため、新たにインメモリDBを導入する。夜間バッチにおける大量データ処理時のIOボトルネックを解消することが目的である。</t>
         </is>
       </c>
     </row>
@@ -553,15 +556,14 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>章・節・項の見出しが示す対象範囲と、その直下に記述されている本文の情報が厳密に対応しており、見出しから推測される期待内容と実際の記述事項に乖離がない。</t>
+          <t>章や節などの見出し名称が、その配下に記述された機能要件やシステム仕様のスコープを正確に表しており、見出しと本文の内容が論理的に合致している。</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】見出し：エラー処理方針
-本文：正常系の画面遷移図を以下に示す（見出しの内容と本文が不一致）。
-→【適合例】見出し：エラー処理方針
-本文：例外発生時のロールバック手順およびユーザー通知の定義を以下に記述する。</t>
+          <t>★新規追加
+【非適合例】見出し「3.1ログイン処理の正常系フロー」の配下に、パスワード間違い時のアカウントロック機能に関する仕様を記述している。（見出しが示すスコープと本文の仕様内容が合致していない。）
+→【適合例】見出し「3.1ログイン処理の正常系フロー」の配下には、正しいIDとパスワードの入力からダッシュボード画面への遷移手順のみを記述している。</t>
         </is>
       </c>
     </row>
@@ -573,13 +575,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>本文中の説明と、それに対応する図表内の構成要素（用語、数値、ステータス、ID等）が完全に一致しており、参照時に情報の齟齬や混乱が生じない状態にある。</t>
+          <t>システム構成図や業務フロー図に記載されたコンポーネント名称および処理経路と、本文中の仕様説明における名称や処理内容の定義を、同一の用語と論理構造を用いて記述している。</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】本文では「ステータスを保留にする」とあるが、状態遷移図内では「一時停止」と記載されている（用語の不一致）。
-→【適合例】本文で解説する「承認待ち」状態への遷移条件は、別紙のワークフロー図に記載された「承認待ち」の定義と一致している。</t>
+          <t>★新規追加
+【非適合例】本文では「注文データは直接決済システムへ送信される」と記述しているが、業務フロー図では注文データが一旦キューを経由する構成として描画されている。（図表の表現と本文の仕様説明に矛盾が生じている。）
+→【適合例】業務フロー図で注文データが一旦キューを経由する構成を描画し、本文でも図表と一致する内容で「注文データは直接送信せず、非同期処理のためのキューを経由して決済システムへ送信する」と記述している。</t>
         </is>
       </c>
     </row>
